--- a/templates/unittest_template.xlsx
+++ b/templates/unittest_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\promptcase-studio\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA1D7FB7-36D1-480E-88BE-4E1321105F63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C491037-53A2-4CCC-A4E3-BE57AA54E196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AD02B665-237F-4D57-887F-DAAC4116AF57}"/>
   </bookViews>
@@ -230,7 +230,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -253,103 +253,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -359,24 +269,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -395,13 +287,16 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -755,44 +650,44 @@
   <sheetData>
     <row r="1" spans="2:7" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="18"/>
-    </row>
-    <row r="3" spans="2:7" s="10" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="9" t="s">
+      <c r="C2" s="13"/>
+    </row>
+    <row r="3" spans="2:7" s="4" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="2:7" s="14" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="11" t="s">
+    <row r="4" spans="2:7" s="8" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13" t="s">
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="13"/>
+      <c r="G4" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -809,72 +704,72 @@
   <sheetFormatPr defaultRowHeight="19.2" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3.19921875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="30.69921875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="26.19921875" style="1" customWidth="1"/>
     <col min="3" max="3" width="120.69921875" style="1" customWidth="1"/>
     <col min="4" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:3" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="2:3" ht="49.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:3" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="3" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="4"/>
+      <c r="C3" s="10"/>
     </row>
     <row r="4" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="10" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="79.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="6"/>
+      <c r="C5" s="10"/>
     </row>
     <row r="6" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="6"/>
+      <c r="C6" s="10"/>
     </row>
     <row r="7" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="6"/>
+      <c r="C7" s="10"/>
     </row>
     <row r="8" spans="2:3" ht="79.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="6"/>
+      <c r="C8" s="10"/>
     </row>
     <row r="9" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="6"/>
+      <c r="C9" s="10"/>
     </row>
     <row r="10" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="6"/>
-    </row>
-    <row r="11" spans="2:3" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B11" s="7" t="s">
+      <c r="C10" s="10"/>
+    </row>
+    <row r="11" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B11" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="8"/>
+      <c r="C11" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -888,34 +783,34 @@
   <sheetFormatPr defaultRowHeight="19.2" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3.19921875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.69921875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.69921875" style="1" customWidth="1"/>
     <col min="3" max="3" width="120.69921875" style="1" customWidth="1"/>
     <col min="4" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:3" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="2:3" ht="49.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:3" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:3" ht="100.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="15" t="s">
+    <row r="3" spans="2:3" ht="225" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B3" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="4"/>
-    </row>
-    <row r="4" spans="2:3" ht="100.05" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="16" t="s">
+      <c r="C3" s="10"/>
+    </row>
+    <row r="4" spans="2:3" ht="90" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="6"/>
-    </row>
-    <row r="5" spans="2:3" ht="199.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B5" s="17" t="s">
+      <c r="C4" s="10"/>
+    </row>
+    <row r="5" spans="2:3" ht="199.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B5" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="8"/>
+      <c r="C5" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/templates/unittest_template.xlsx
+++ b/templates/unittest_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\promptcase-studio\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C491037-53A2-4CCC-A4E3-BE57AA54E196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BA8E1BD-5D75-4E91-81FA-8F050DF0E514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AD02B665-237F-4D57-887F-DAAC4116AF57}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>[테스트 결과]</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -84,18 +84,6 @@
   </si>
   <si>
     <t>변경구분</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Program</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>채산관리시스템</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>요건 변경에 따른 개발 프로그램 수정</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -676,17 +664,11 @@
       </c>
     </row>
     <row r="4" spans="2:7" s="8" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>11</v>
-      </c>
+      <c r="B4" s="5"/>
+      <c r="C4" s="6"/>
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
-      <c r="F4" s="7" t="s">
-        <v>13</v>
-      </c>
+      <c r="F4" s="7"/>
       <c r="G4" s="7"/>
     </row>
   </sheetData>
@@ -712,62 +694,62 @@
     <row r="1" spans="2:3" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:3" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" s="9" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C3" s="10"/>
     </row>
     <row r="4" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="79.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C5" s="10"/>
     </row>
     <row r="6" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="9" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C6" s="10"/>
     </row>
     <row r="7" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="9" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C7" s="10"/>
     </row>
     <row r="8" spans="2:3" ht="79.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="9" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C8" s="10"/>
     </row>
     <row r="9" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B9" s="9" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C9" s="10"/>
     </row>
     <row r="10" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="9" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C10" s="10"/>
     </row>
     <row r="11" spans="2:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="9" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C11" s="10"/>
     </row>

--- a/templates/unittest_template.xlsx
+++ b/templates/unittest_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\promptcase-studio\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BA8E1BD-5D75-4E91-81FA-8F050DF0E514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{487AE85C-582A-46B1-A55F-820AD50C1A1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AD02B665-237F-4D57-887F-DAAC4116AF57}"/>
   </bookViews>
@@ -628,10 +628,11 @@
   <sheetFormatPr defaultRowHeight="19.2" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3.19921875" style="1" customWidth="1"/>
-    <col min="2" max="3" width="15.69921875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.69921875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.69921875" style="1" customWidth="1"/>
     <col min="4" max="4" width="30.69921875" style="1" customWidth="1"/>
     <col min="5" max="5" width="40.69921875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="35.69921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="45.69921875" style="1" customWidth="1"/>
     <col min="7" max="7" width="10.69921875" style="1" customWidth="1"/>
     <col min="8" max="16384" width="8.796875" style="1"/>
   </cols>
